--- a/public/docs/Plantilla Cursos OMI.xlsx
+++ b/public/docs/Plantilla Cursos OMI.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{CA0DF289-812C-4A80-9619-3FA7781A1181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF90BDC8-F7A1-46E4-A4C4-5392CB9F38BD}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{CA0DF289-812C-4A80-9619-3FA7781A1181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF31AD8-9595-4B48-B2D4-F5CB863812FB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="People" sheetId="1" r:id="rId1"/>
-    <sheet name="Parameters" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Parameters" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Parameters!$J$13:$K$75</definedName>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="402">
   <si>
     <t>Obligatorio</t>
   </si>
@@ -1251,6 +1251,9 @@
   </si>
   <si>
     <t>TELEFONO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -3758,23 +3761,6 @@
             <a:t>TEXTO CERTIFICADO</a:t>
           </a:r>
         </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>(Elegir)</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO" sz="1100" b="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -3848,17 +3834,6 @@
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>TEXTO CERTIFICADO EN INGLÉS</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>(Elegir)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -16199,7 +16174,7 @@
       <c r="AG312" s="25"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8E5wLVSe865oSKq6o/F91ZNz7gYkXGar2rv0uCnuqdPBcRMBCO+qpmhggtZNWS3zkuM8K1zvtbZFIMTtWG2bmw==" saltValue="RdYBYntmJ0tX2IYJDg7B6A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7S0xI++BbAeLT+DZmMu27P6LWe4JmnmJ8tsJ1GgNgVnYc20omZ3Etqj4+297Wmux5LWFVnx9CMb93R3El/Xnmw==" saltValue="NBoiKinEfF6C4vcBoA9XKQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="H24:O24 S25:U30 S39:U39 W39:X39 AA15:AA23 AA39 AE15:AG23 AA25:AA30 AE25:AG419 Z31:AD38 Z40:AD419 H3:O14 W3:X30 A15:U23 A25:R419 S40:Y419 S31:Y38" name="Rango1"/>
     <protectedRange sqref="A24:B24 A3:B14" name="Rango1_1"/>
@@ -16224,7 +16199,7 @@
       <formula1>0</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E24 E3:E14 AA11:AA14 G24 AA24 V39 Z39 V11:V30 G3:G14 Z11:Z30" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G14 Z11:Z30 AA11:AA14 G24 AA24 V39 Z39 V11:V30" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16240,15 +16215,6 @@
             <xm:f>0</xm:f>
           </x14:formula2>
           <xm:sqref>I3 I5</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
-          <x14:formula1>
-            <xm:f>Parameters!$D$4:$D$238</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>E15:E23 E25:E202</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
@@ -16280,6 +16246,12 @@
           </x14:formula1>
           <xm:sqref>X3:X1048576</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3C3FA703-5F30-487A-9556-657F8B393F2B}">
+          <x14:formula1>
+            <xm:f>Parameters!$D$4:$D$196</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E1048576</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -16291,22 +16263,22 @@
   <dimension ref="A1:N196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="33.59765625" customWidth="1"/>
-    <col min="5" max="6" width="10.5" customWidth="1"/>
+    <col min="1" max="3" width="10.5" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="33.59765625" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="10.5" hidden="1" customWidth="1"/>
+    <col min="7" max="9" width="0" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="10.5" customWidth="1"/>
-    <col min="12" max="12" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.796875" customWidth="1"/>
     <col min="13" max="13" width="59.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" s="57" t="s">
         <v>399</v>
       </c>
       <c r="B1" s="57"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="H2" s="61"/>
       <c r="I2" s="61"/>
     </row>
@@ -16346,6 +16318,9 @@
       <c r="K4" t="s">
         <v>255</v>
       </c>
+      <c r="L4" t="s">
+        <v>401</v>
+      </c>
       <c r="M4" t="s">
         <v>350</v>
       </c>
@@ -16369,6 +16344,9 @@
       <c r="K5" t="s">
         <v>373</v>
       </c>
+      <c r="L5" t="s">
+        <v>401</v>
+      </c>
       <c r="M5" t="s">
         <v>392</v>
       </c>
@@ -16389,6 +16367,9 @@
       <c r="K6" t="s">
         <v>256</v>
       </c>
+      <c r="L6" t="s">
+        <v>401</v>
+      </c>
       <c r="M6" t="s">
         <v>360</v>
       </c>
@@ -16409,6 +16390,9 @@
       <c r="K7" t="s">
         <v>257</v>
       </c>
+      <c r="L7" t="s">
+        <v>401</v>
+      </c>
       <c r="M7" t="s">
         <v>378</v>
       </c>
@@ -16425,6 +16409,9 @@
       </c>
       <c r="K8" t="s">
         <v>398</v>
+      </c>
+      <c r="L8" t="s">
+        <v>401</v>
       </c>
       <c r="M8" t="s">
         <v>377</v>

--- a/public/docs/Plantilla Cursos OMI.xlsx
+++ b/public/docs/Plantilla Cursos OMI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{CA0DF289-812C-4A80-9619-3FA7781A1181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF31AD8-9595-4B48-B2D4-F5CB863812FB}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{CA0DF289-812C-4A80-9619-3FA7781A1181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67C65C1B-B197-402A-A104-CF9BF2F535CB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Parameters!$J$13:$K$75</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -672,10 +683,6 @@
   </si>
   <si>
     <t>Opcional
-Fecha de nacimiento</t>
-  </si>
-  <si>
-    <t>Opcional
 Fecha Inicio</t>
   </si>
   <si>
@@ -706,9 +713,6 @@
     <t>docformato</t>
   </si>
   <si>
-    <t>fechanacimiento</t>
-  </si>
-  <si>
     <t>fechainicio</t>
   </si>
   <si>
@@ -1254,6 +1258,13 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>fechanacimiento2</t>
+  </si>
+  <si>
+    <t>Opcional
+Fecha de nacimiento2</t>
   </si>
 </sst>
 </file>
@@ -4252,9 +4263,9 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
@@ -4276,8 +4287,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17655540" y="0"/>
-          <a:ext cx="1501140" cy="449580"/>
+          <a:off x="11178988" y="546847"/>
+          <a:ext cx="1497106" cy="448235"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5088,6 +5099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AG312"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5168,58 +5180,58 @@
         <v>212</v>
       </c>
       <c r="P1" s="45" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q1" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="R1" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="Q1" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="R1" s="45" t="s">
+      <c r="S1" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="T1" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="U1" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="S1" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="T1" s="45" t="s">
+      <c r="V1" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="W1" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="X1" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="Y1" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z1" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA1" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="U1" s="45" t="s">
+      <c r="AB1" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="AC1" s="45" t="s">
         <v>215</v>
       </c>
-      <c r="V1" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="W1" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="X1" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y1" s="45" t="s">
-        <v>233</v>
-      </c>
-      <c r="Z1" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA1" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="AB1" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="AC1" s="45" t="s">
+      <c r="AD1" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="AE1" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="AF1" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="AD1" s="45" t="s">
-        <v>240</v>
-      </c>
-      <c r="AE1" s="26" t="s">
+      <c r="AG1" s="13" t="s">
         <v>218</v>
-      </c>
-      <c r="AF1" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="AG1" s="13" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5230,7 +5242,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>4</v>
@@ -5266,61 +5278,61 @@
         <v>14</v>
       </c>
       <c r="O2" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="R2" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="S2" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="T2" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="U2" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="V2" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="X2" s="51" t="s">
         <v>230</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="Y2" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="AA2" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC2" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="S2" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="T2" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="U2" s="38" t="s">
+      <c r="AD2" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="V2" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="X2" s="51" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA2" s="47" t="s">
-        <v>248</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC2" s="11" t="s">
+      <c r="AE2" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="AF2" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="AD2" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="AE2" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="AF2" s="31" t="s">
+      <c r="AG2" s="14" t="s">
         <v>227</v>
-      </c>
-      <c r="AG2" s="14" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -16174,9 +16186,9 @@
       <c r="AG312" s="25"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7S0xI++BbAeLT+DZmMu27P6LWe4JmnmJ8tsJ1GgNgVnYc20omZ3Etqj4+297Wmux5LWFVnx9CMb93R3El/Xnmw==" saltValue="NBoiKinEfF6C4vcBoA9XKQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ugu95iz3nbCdM01hRKSHNN497alxzZx7rF5omDgT/ooxBkj+FVv5yygDtAsPMIbMdBqSaS+18dpVXPL7zq4+Ow==" saltValue="gSgvSe1a8Lzj1kj6T28wKg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="H24:O24 S25:U30 S39:U39 W39:X39 AA15:AA23 AA39 AE15:AG23 AA25:AA30 AE25:AG419 Z31:AD38 Z40:AD419 H3:O14 W3:X30 A15:U23 A25:R419 S40:Y419 S31:Y38" name="Rango1"/>
+    <protectedRange sqref="H24:O24 S25:U30 S39:U39 W39:X39 AA15:AA23 AA39 AE15:AG23 AA25:AA30 AE25:AG419 H3:O14 W3:X30 A15:U23 A25:R419 S40:AD419 S31:AD38" name="Rango1"/>
     <protectedRange sqref="A24:B24 A3:B14" name="Rango1_1"/>
     <protectedRange sqref="C24:D24 C3:D14" name="Rango1_3"/>
     <protectedRange sqref="E24:F24 E3:F14" name="Rango1_4"/>
@@ -16260,6 +16272,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:N196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16274,7 +16287,7 @@
   <sheetData>
     <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" s="57" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B1" s="57"/>
     </row>
@@ -16290,16 +16303,16 @@
         <v>18</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -16310,22 +16323,22 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N4" s="52" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -16336,22 +16349,22 @@
         <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -16359,22 +16372,22 @@
         <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N6" s="52" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -16382,22 +16395,22 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="N7" s="52" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -16405,19 +16418,19 @@
         <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K8" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N8" s="52" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -16425,10 +16438,10 @@
         <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="N9" s="52" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -16436,10 +16449,10 @@
         <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="N10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -16447,7 +16460,7 @@
         <v>27</v>
       </c>
       <c r="M11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="N11" s="54"/>
     </row>
@@ -16456,7 +16469,7 @@
         <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N12" s="54"/>
     </row>
@@ -16465,7 +16478,7 @@
         <v>29</v>
       </c>
       <c r="M13" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N13" s="54"/>
     </row>
@@ -16474,7 +16487,7 @@
         <v>30</v>
       </c>
       <c r="M14" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="N14" s="54"/>
     </row>
@@ -16483,10 +16496,10 @@
         <v>31</v>
       </c>
       <c r="M15" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N15" s="52" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -16494,10 +16507,10 @@
         <v>32</v>
       </c>
       <c r="M16" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N16" s="52" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="4:14" x14ac:dyDescent="0.3">
@@ -16505,10 +16518,10 @@
         <v>33</v>
       </c>
       <c r="M17" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="4:14" x14ac:dyDescent="0.3">
@@ -16516,7 +16529,7 @@
         <v>34</v>
       </c>
       <c r="M18" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N18" s="54"/>
     </row>
@@ -16525,10 +16538,10 @@
         <v>35</v>
       </c>
       <c r="M19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N19" s="52" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="4:14" x14ac:dyDescent="0.3">
@@ -16536,10 +16549,10 @@
         <v>36</v>
       </c>
       <c r="M20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N20" s="52" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="4:14" x14ac:dyDescent="0.3">
@@ -16547,10 +16560,10 @@
         <v>37</v>
       </c>
       <c r="M21" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="N21" s="52" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="4:14" x14ac:dyDescent="0.3">
@@ -16558,10 +16571,10 @@
         <v>38</v>
       </c>
       <c r="M22" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N22" s="52" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" spans="4:14" x14ac:dyDescent="0.3">
@@ -16569,10 +16582,10 @@
         <v>39</v>
       </c>
       <c r="M23" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="N23" s="52" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="4:14" x14ac:dyDescent="0.3">
@@ -16580,10 +16593,10 @@
         <v>40</v>
       </c>
       <c r="M24" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N24" s="52" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="4:14" x14ac:dyDescent="0.3">
@@ -16591,10 +16604,10 @@
         <v>41</v>
       </c>
       <c r="M25" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N25" s="52" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="4:14" x14ac:dyDescent="0.3">
@@ -16602,10 +16615,10 @@
         <v>42</v>
       </c>
       <c r="M26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N26" s="52" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="4:14" x14ac:dyDescent="0.3">
@@ -16613,10 +16626,10 @@
         <v>43</v>
       </c>
       <c r="M27" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="N27" s="52" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" spans="4:14" x14ac:dyDescent="0.3">
@@ -16624,10 +16637,10 @@
         <v>44</v>
       </c>
       <c r="M28" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N28" s="52" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="4:14" x14ac:dyDescent="0.3">
@@ -16635,10 +16648,10 @@
         <v>45</v>
       </c>
       <c r="M29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="N29" s="52" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="4:14" x14ac:dyDescent="0.3">
@@ -16646,10 +16659,10 @@
         <v>46</v>
       </c>
       <c r="M30" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N30" s="52" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="4:14" x14ac:dyDescent="0.3">
@@ -16657,10 +16670,10 @@
         <v>47</v>
       </c>
       <c r="M31" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N31" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="4:14" x14ac:dyDescent="0.3">
@@ -16668,24 +16681,24 @@
         <v>48</v>
       </c>
       <c r="M32" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N32" s="52" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
       </c>
       <c r="M33" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="N33" s="52" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.3">
@@ -16693,10 +16706,10 @@
         <v>49</v>
       </c>
       <c r="M34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N34" s="52" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.3">
@@ -16704,10 +16717,10 @@
         <v>50</v>
       </c>
       <c r="M35" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N35" s="52" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.3">
@@ -16715,10 +16728,10 @@
         <v>51</v>
       </c>
       <c r="M36" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N36" s="52" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.3">
@@ -16726,10 +16739,10 @@
         <v>52</v>
       </c>
       <c r="M37" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N37" s="52" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.3">
@@ -16737,24 +16750,24 @@
         <v>53</v>
       </c>
       <c r="M38" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N38" s="52" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D39" t="s">
         <v>54</v>
       </c>
       <c r="M39" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="N39" s="52" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.3">
@@ -16762,24 +16775,24 @@
         <v>55</v>
       </c>
       <c r="M40" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="N40" s="52" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D41" t="s">
         <v>56</v>
       </c>
       <c r="M41" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N41" s="52" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.3">
@@ -16787,10 +16800,10 @@
         <v>211</v>
       </c>
       <c r="M42" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N42" s="52" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.3">
@@ -16798,10 +16811,10 @@
         <v>57</v>
       </c>
       <c r="M43" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N43" s="52" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" spans="3:14" x14ac:dyDescent="0.3">
@@ -16809,10 +16822,10 @@
         <v>58</v>
       </c>
       <c r="M44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N44" s="52" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45" spans="3:14" x14ac:dyDescent="0.3">
@@ -16820,10 +16833,10 @@
         <v>59</v>
       </c>
       <c r="M45" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N45" s="52" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" spans="3:14" x14ac:dyDescent="0.3">
@@ -16831,10 +16844,10 @@
         <v>60</v>
       </c>
       <c r="M46" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N46" s="52" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" spans="3:14" x14ac:dyDescent="0.3">
@@ -16842,10 +16855,10 @@
         <v>61</v>
       </c>
       <c r="M47" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="N47" s="52" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="3:14" x14ac:dyDescent="0.3">
@@ -16853,10 +16866,10 @@
         <v>62</v>
       </c>
       <c r="M48" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N48" s="52" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="4:14" x14ac:dyDescent="0.3">
@@ -16864,10 +16877,10 @@
         <v>63</v>
       </c>
       <c r="M49" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="N49" s="52" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="4:14" x14ac:dyDescent="0.3">
@@ -16875,10 +16888,10 @@
         <v>64</v>
       </c>
       <c r="M50" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="N50" s="52" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="4:14" x14ac:dyDescent="0.3">
@@ -16886,10 +16899,10 @@
         <v>65</v>
       </c>
       <c r="M51" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N51" s="52" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="4:14" x14ac:dyDescent="0.3">
@@ -16897,10 +16910,10 @@
         <v>66</v>
       </c>
       <c r="M52" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N52" s="52" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="4:14" x14ac:dyDescent="0.3">
@@ -16908,10 +16921,10 @@
         <v>67</v>
       </c>
       <c r="M53" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N53" s="52" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="4:14" x14ac:dyDescent="0.3">
@@ -16919,10 +16932,10 @@
         <v>68</v>
       </c>
       <c r="M54" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="N54" s="52" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="55" spans="4:14" x14ac:dyDescent="0.3">
@@ -16930,10 +16943,10 @@
         <v>69</v>
       </c>
       <c r="M55" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N55" s="52" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="4:14" x14ac:dyDescent="0.3">
@@ -16941,10 +16954,10 @@
         <v>70</v>
       </c>
       <c r="M56" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="N56" s="52" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="4:14" x14ac:dyDescent="0.3">
@@ -16952,10 +16965,10 @@
         <v>71</v>
       </c>
       <c r="M57" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="N57" s="52" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="4:14" x14ac:dyDescent="0.3">
@@ -16963,10 +16976,10 @@
         <v>72</v>
       </c>
       <c r="M58" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="N58" s="52" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="4:14" x14ac:dyDescent="0.3">
@@ -16974,10 +16987,10 @@
         <v>73</v>
       </c>
       <c r="M59" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N59" s="52" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="4:14" x14ac:dyDescent="0.3">
@@ -16985,10 +16998,10 @@
         <v>74</v>
       </c>
       <c r="M60" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="N60" s="52" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="4:14" x14ac:dyDescent="0.3">
@@ -16996,10 +17009,10 @@
         <v>75</v>
       </c>
       <c r="M61" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N61" s="52" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="4:14" x14ac:dyDescent="0.3">
@@ -17007,10 +17020,10 @@
         <v>76</v>
       </c>
       <c r="M62" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="N62" s="52" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="4:14" x14ac:dyDescent="0.3">
@@ -17018,10 +17031,10 @@
         <v>77</v>
       </c>
       <c r="M63" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N63" s="52" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="64" spans="4:14" x14ac:dyDescent="0.3">
@@ -17029,10 +17042,10 @@
         <v>78</v>
       </c>
       <c r="M64" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="N64" s="52" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="65" spans="4:14" x14ac:dyDescent="0.3">
@@ -17040,10 +17053,10 @@
         <v>79</v>
       </c>
       <c r="M65" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N65" s="52" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="4:14" x14ac:dyDescent="0.3">
@@ -17051,10 +17064,10 @@
         <v>80</v>
       </c>
       <c r="M66" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="N66" s="52" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" spans="4:14" x14ac:dyDescent="0.3">
@@ -17062,10 +17075,10 @@
         <v>81</v>
       </c>
       <c r="M67" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N67" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="68" spans="4:14" x14ac:dyDescent="0.3">
@@ -17073,10 +17086,10 @@
         <v>82</v>
       </c>
       <c r="M68" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N68" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="69" spans="4:14" x14ac:dyDescent="0.3">
@@ -17084,10 +17097,10 @@
         <v>83</v>
       </c>
       <c r="M69" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N69" s="52" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" spans="4:14" x14ac:dyDescent="0.3">
@@ -17095,10 +17108,10 @@
         <v>84</v>
       </c>
       <c r="M70" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="N70" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71" spans="4:14" x14ac:dyDescent="0.3">
@@ -17106,10 +17119,10 @@
         <v>85</v>
       </c>
       <c r="M71" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="N71" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="72" spans="4:14" x14ac:dyDescent="0.3">
@@ -17117,10 +17130,10 @@
         <v>86</v>
       </c>
       <c r="M72" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="N72" s="52" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="73" spans="4:14" x14ac:dyDescent="0.3">
